--- a/output/pdf_financials_xlsx/ALM.xlsx
+++ b/output/pdf_financials_xlsx/ALM.xlsx
@@ -6185,19 +6185,19 @@
         <v>0.1034</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.219751</v>
+        <v>0.057435</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.183108</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.156596</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.103253</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.07375900000000001</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -20628,7 +20628,11 @@
           <t>Share-Based Payment Reserves</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -21572,7 +21576,11 @@
           <t>Share-Based Payment Reserves</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -23590,7 +23598,11 @@
           <t>Share-Based Payment Reserves 183,108</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ALM.xlsx
+++ b/output/pdf_financials_xlsx/ALM.xlsx
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001208</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>-0.873068</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.72153</v>
+        <v>-0.722738</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.429613</v>
@@ -2195,7 +2195,7 @@
         <v>-0.86544</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.71089</v>
+        <v>-0.712098</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.424256</v>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002221</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.027654</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.027654</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.373489</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.00287</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002813</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000176</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.016337</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.051561</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.005026</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000648</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000762</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.00104</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.000212</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.006489</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
     </row>
     <row r="35">
@@ -2625,58 +2625,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002221</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.027654</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.027654</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.373489</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.00287</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002813</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000176</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.016337</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.051561</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.005026</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000648</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000762</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.00104</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.000212</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.006489</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
     </row>
     <row r="37">
@@ -3357,58 +3357,58 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.002656</v>
+        <v>0.000435</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.033743</v>
+        <v>0.006089</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.033743</v>
+        <v>0.006089</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.571219</v>
+        <v>0.19773</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.056447</v>
+        <v>0.053577</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.008741000000000001</v>
+        <v>0.005928</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.00291</v>
+        <v>0.002734</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.020242</v>
+        <v>0.003905</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.054454</v>
+        <v>0.002893</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.009466</v>
+        <v>0.00444</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.00462</v>
+        <v>0.003858</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.005658</v>
+        <v>0.004618</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.004722</v>
+        <v>0.00447</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.011084</v>
+        <v>0.004595</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.003721</v>
+        <v>0.003401</v>
       </c>
     </row>
     <row r="49">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -22428,7 +22428,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -35974,7 +35974,11 @@
           <t>Unrealized Foreign Exchange Gain on Reclamation Deposit</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -37024,7 +37028,11 @@
           <t>Unrealized Foreign Exchange Gain (Loss) on Reclamation Deposit</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E272" s="5" t="n">
         <v>-0.000839</v>
       </c>
@@ -37998,7 +38006,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -43650,7 +43658,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
